--- a/data/hex_xlsx/ELEAV.HE.xlsx
+++ b/data/hex_xlsx/ELEAV.HE.xlsx
@@ -8285,12 +8285,30 @@
       <c r="O38" s="18">
         <v>88.9</v>
       </c>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
+      <c r="P38" s="18">
+        <f t="shared" ref="P38:U38" si="1">P39+P40+P43+P47+P49+P36</f>
+        <v>97.02</v>
+      </c>
+      <c r="Q38" s="18">
+        <f t="shared" si="1"/>
+        <v>103.49</v>
+      </c>
+      <c r="R38" s="18">
+        <f t="shared" si="1"/>
+        <v>112.61</v>
+      </c>
+      <c r="S38" s="18">
+        <f t="shared" si="1"/>
+        <v>135.66</v>
+      </c>
+      <c r="T38" s="18">
+        <f t="shared" si="1"/>
+        <v>92.15</v>
+      </c>
+      <c r="U38" s="18">
+        <f t="shared" si="1"/>
+        <v>99.83</v>
+      </c>
       <c r="V38" s="18">
         <v>89.05</v>
       </c>
@@ -9443,18 +9461,42 @@
       <c r="K66" s="18">
         <v>40.99</v>
       </c>
-      <c r="L66" s="20"/>
-      <c r="M66" s="20"/>
-      <c r="N66" s="20"/>
-      <c r="O66" s="20"/>
-      <c r="P66" s="20"/>
-      <c r="Q66" s="20"/>
-      <c r="R66" s="20"/>
-      <c r="S66" s="20"/>
-      <c r="T66" s="20"/>
-      <c r="U66" s="20"/>
-      <c r="V66" s="20"/>
-      <c r="W66" s="20"/>
+      <c r="L66" s="18">
+        <v>66.7</v>
+      </c>
+      <c r="M66" s="18">
+        <v>75.98</v>
+      </c>
+      <c r="N66" s="18">
+        <v>68.18</v>
+      </c>
+      <c r="O66" s="18">
+        <v>59.13</v>
+      </c>
+      <c r="P66" s="18">
+        <v>70.14</v>
+      </c>
+      <c r="Q66" s="18">
+        <v>75.5</v>
+      </c>
+      <c r="R66" s="18">
+        <v>63.2</v>
+      </c>
+      <c r="S66" s="18">
+        <v>91.73</v>
+      </c>
+      <c r="T66" s="18">
+        <v>51.04</v>
+      </c>
+      <c r="U66" s="18">
+        <v>45.28</v>
+      </c>
+      <c r="V66" s="18">
+        <v>50.44</v>
+      </c>
+      <c r="W66" s="18">
+        <v>55.51</v>
+      </c>
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
